--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/9945-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/9945-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1345B4A-254C-4EA8-8469-A97E507F39FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8FBC42D-40F9-47DC-B3CD-B77F9DD21505}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{4CEB1F66-6EC7-4E18-9F9D-386062801C67}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{EBD78D7A-7E4B-4961-9762-2E488B3780DD}"/>
   </bookViews>
   <sheets>
     <sheet name="9945-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1577,27 +1577,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4309851-4600-4900-9A50-6F796BAE5EE0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB32D047-970C-4F11-83D2-989AF8B8C0F3}">
   <dimension ref="A1:X47"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1631,7 +1630,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1667,7 +1666,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1719,7 +1718,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1787,7 +1786,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2024</v>
       </c>
@@ -1859,7 +1858,7 @@
         <v>3.84</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40">
         <v>2023</v>
       </c>
@@ -1931,7 +1930,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2022</v>
       </c>
@@ -2003,7 +2002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="42">
         <v>2021</v>
       </c>
@@ -2075,7 +2074,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="44"/>
       <c r="B9" s="45"/>
       <c r="C9" s="18" t="s">
@@ -2103,7 +2102,7 @@
       <c r="W9" s="51"/>
       <c r="X9" s="47"/>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="52">
         <v>2020</v>
       </c>
@@ -2175,7 +2174,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="54"/>
       <c r="B11" s="55"/>
       <c r="C11" s="20" t="s">
@@ -2203,7 +2202,7 @@
       <c r="W11" s="61"/>
       <c r="X11" s="57"/>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="42">
         <v>2019</v>
       </c>
@@ -2275,7 +2274,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="44"/>
       <c r="B13" s="45"/>
       <c r="C13" s="18" t="s">
@@ -2303,7 +2302,7 @@
       <c r="W13" s="51"/>
       <c r="X13" s="47"/>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="38">
         <v>2018</v>
       </c>
@@ -2375,7 +2374,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="40">
         <v>2017</v>
       </c>
@@ -2447,7 +2446,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="38">
         <v>2016</v>
       </c>
@@ -2519,7 +2518,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="40">
         <v>2015</v>
       </c>
@@ -2591,7 +2590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="38">
         <v>2014</v>
       </c>
@@ -2663,7 +2662,7 @@
         <v>13.8</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="40">
         <v>2013</v>
       </c>
@@ -2735,7 +2734,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="38">
         <v>2012</v>
       </c>
@@ -2807,7 +2806,7 @@
         <v>5.74</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="40">
         <v>2011</v>
       </c>
@@ -2879,7 +2878,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="38">
         <v>2010</v>
       </c>
@@ -2951,7 +2950,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="40">
         <v>2009</v>
       </c>
@@ -3023,7 +3022,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="38">
         <v>2008</v>
       </c>
@@ -3095,7 +3094,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="40">
         <v>2007</v>
       </c>
@@ -3167,7 +3166,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="38">
         <v>2006</v>
       </c>
@@ -3239,7 +3238,7 @@
         <v>9.09</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="40">
         <v>2005</v>
       </c>
@@ -3311,7 +3310,7 @@
         <v>11.4</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="38">
         <v>2004</v>
       </c>
@@ -3383,7 +3382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="40">
         <v>2003</v>
       </c>
@@ -3455,7 +3454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="38">
         <v>2002</v>
       </c>
@@ -3527,7 +3526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="40">
         <v>2001</v>
       </c>
@@ -3599,7 +3598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="38">
         <v>2000</v>
       </c>
@@ -3671,7 +3670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="40">
         <v>1999</v>
       </c>
@@ -3743,7 +3742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="38">
         <v>1998</v>
       </c>
@@ -3815,7 +3814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="40">
         <v>1997</v>
       </c>
@@ -3887,7 +3886,7 @@
         <v>9.85</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="38">
         <v>1996</v>
       </c>
@@ -3959,7 +3958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="40">
         <v>1995</v>
       </c>
@@ -4031,7 +4030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="38">
         <v>1994</v>
       </c>
@@ -4103,7 +4102,7 @@
         <v>9.49</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="40">
         <v>1993</v>
       </c>
@@ -4175,7 +4174,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="52">
         <v>1992</v>
       </c>
@@ -4247,7 +4246,7 @@
         <v>15.3</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="54"/>
       <c r="B41" s="55"/>
       <c r="C41" s="20" t="s">
@@ -4275,7 +4274,7 @@
       <c r="W41" s="61"/>
       <c r="X41" s="57"/>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="40">
         <v>1991</v>
       </c>
@@ -4347,7 +4346,7 @@
         <v>8.39</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="52">
         <v>1990</v>
       </c>
@@ -4419,7 +4418,7 @@
         <v>3.14</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="54"/>
       <c r="B44" s="55"/>
       <c r="C44" s="20" t="s">
@@ -4447,7 +4446,7 @@
       <c r="W44" s="61"/>
       <c r="X44" s="57"/>
     </row>
-    <row r="45" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="40">
         <v>1989</v>
       </c>
@@ -4519,7 +4518,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="38">
         <v>1988</v>
       </c>
@@ -4591,7 +4590,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="40" t="s">
         <v>58</v>
       </c>
